--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4178,8 +4285,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4198,1122 +4309,1115 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">궁초댕기 — 민요채보-1/궁초댕기.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">궁초댕기</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="C3" s="13"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="13"/>
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">궁</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="14"/>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">같</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="J5" s="12"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="N5" s="12"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">댕</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="15"/>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">／
 汰</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 汰</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 汰</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="E7" s="13"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P7" s="12"/>
+      <c r="Q7" s="13"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">테</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="P8" s="12"/>
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H9" s="12"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">때</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">때</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="15"/>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="G10" s="15"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="13"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">뭉</t>
         </is>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="J11" s="12"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="N11" s="12"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="13"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="14"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">글</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M12" s="14"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">때</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="N13" s="12"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="F14" s="12"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">벼</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="M14" s="15"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="15"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">숨</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="14"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="14"/>
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="14"/>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="K16" s="14"/>
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M16" s="14"/>
+      <c r="N16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q16" s="2"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="14"/>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="14"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="14"/>
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="14"/>
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K17" s="14"/>
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲
 汰</t>
-        </is>
-      </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="O17" s="14"/>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲
 汰</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="E18" s="15"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K18" s="15"/>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O18" s="15"/>
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q18" s="2"/>
+      <c r="Q18" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -255,11 +255,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -3908,10 +3904,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s=""/>
-      <c r="B1" s="">
-        <v>0</v>
-      </c>
+      <c r="A1" s="0"/>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -549,13 +549,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―</t>
+          <t xml:space="preserve">㳞|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―</t>
+          <t xml:space="preserve">㳞|–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -707,13 +707,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―</t>
+          <t xml:space="preserve">㳞|–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -909,12 +909,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -1019,13 +1019,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I19" s="2"/>
@@ -1446,13 +1446,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I38" s="2"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I40" s="2"/>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2718,13 +2718,13 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―</t>
+          <t xml:space="preserve">仲|–</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I63" s="2"/>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -3420,13 +3420,13 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3688,13 +3688,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -3829,12 +3829,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I89" s="2"/>
@@ -3951,7 +3951,7 @@
       <c r="F3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
@@ -3982,7 +3982,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -4004,7 +4004,7 @@
       <c r="P3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="Q3" s="8" t="inlineStr">
@@ -4019,7 +4019,7 @@
       <c r="C4" s="9"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
@@ -4049,7 +4049,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="9"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="9"/>
@@ -4130,7 +4130,7 @@
       <c r="P5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       <c r="K6" s="10"/>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M6" s="10"/>
@@ -4230,7 +4230,7 @@
       <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="O7" s="8" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="9"/>
@@ -4267,7 +4267,7 @@
       <c r="K8" s="9"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M8" s="9"/>
@@ -4288,7 +4288,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="9"/>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G9" s="9"/>
@@ -4370,7 +4370,7 @@
       <c r="M10" s="10"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4385,7 +4385,7 @@
       <c r="D11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="8"/>
@@ -4451,7 +4451,7 @@
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="9"/>
@@ -4463,13 +4463,13 @@
       <c r="K12" s="9"/>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O12" s="9"/>
@@ -4493,13 +4493,13 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
@@ -4540,7 +4540,7 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="10"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G15" s="8"/>
@@ -4619,7 +4619,7 @@
       <c r="P15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -4646,7 +4646,7 @@
       <c r="G16" s="9"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="9"/>
@@ -4658,7 +4658,7 @@
       <c r="K16" s="9"/>
       <c r="L16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M16" s="9"/>
@@ -4699,13 +4699,13 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="9"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="P17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="D18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="E18" s="10"/>
@@ -4779,7 +4779,7 @@
       <c r="K18" s="10"/>
       <c r="L18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M18" s="10"/>

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3908,106 +3946,106 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">궁초댕기</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">신고</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">웃</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">신고</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">궁</t>
         </is>
@@ -4015,50 +4053,50 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="B4" s="21"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㴌</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="J4" s="21"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
@@ -4066,74 +4104,74 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="25"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으며</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">댕</t>
         </is>
@@ -4141,38 +4179,38 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="B6" s="21"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="E6" s="27"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M6" s="27"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="27"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="Q6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -4180,449 +4218,449 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">열두</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="I7" s="22"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오리</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="8"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="B8" s="21"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G8" s="25"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M8" s="25"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="O8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">올</t>
         </is>
       </c>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="9"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="I9" s="25"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="O9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">때는</t>
         </is>
       </c>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="9"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="27"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="10"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">무슨</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한아</t>
         </is>
       </c>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="8"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="9"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M12" s="25"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O12" s="25"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">숨에</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">름</t>
         </is>
       </c>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="9"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="10"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">올</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무슨</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃을</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
@@ -4630,54 +4668,54 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랐</t>
         </is>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="F16" s="21"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="K16" s="25"/>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M16" s="25"/>
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O16" s="9" t="inlineStr">
+      <c r="O16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="P16" s="18" t="inlineStr">
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q16" s="12" t="inlineStr">
+      <c r="Q16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -4685,64 +4723,64 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="K17" s="25"/>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">짝에</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr">
+      <c r="Q17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4750,47 +4788,47 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="27"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="27"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="K18" s="27"/>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M18" s="27"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="Q18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -3923,28 +3923,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3967,11 +3967,11 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -4102,11 +4102,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="25"/>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="27"/>
@@ -4216,11 +4216,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="22"/>
@@ -4279,7 +4279,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -4322,7 +4322,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       <c r="K10" s="27"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4416,7 +4416,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4475,7 +4475,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -4495,7 +4495,7 @@
       <c r="I12" s="25"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="25"/>
@@ -4514,7 +4514,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -4543,7 +4543,7 @@
       <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
@@ -4572,7 +4572,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="27"/>
@@ -4607,7 +4607,7 @@
       <c r="P14" s="21"/>
       <c r="Q14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -4690,7 +4690,7 @@
       <c r="I16" s="25"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K16" s="25"/>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="27"/>

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -3983,7 +3983,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고</t>
+          <t xml:space="preserve">신
+고</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
@@ -4036,7 +4037,8 @@
       </c>
       <c r="O3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고</t>
+          <t xml:space="preserve">신
+고</t>
         </is>
       </c>
       <c r="P3" s="21" t="inlineStr">
@@ -4151,7 +4153,8 @@
       </c>
       <c r="M5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">으며</t>
+          <t xml:space="preserve">으
+며</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
@@ -4232,7 +4235,8 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">열두</t>
+          <t xml:space="preserve">열
+두</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -4262,7 +4266,8 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">오리</t>
+          <t xml:space="preserve">오
+리</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -4373,7 +4378,8 @@
       </c>
       <c r="O9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">때는</t>
+          <t xml:space="preserve">때
+는</t>
         </is>
       </c>
       <c r="P9" s="21"/>
@@ -4458,7 +4464,8 @@
       </c>
       <c r="M11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">무슨</t>
+          <t xml:space="preserve">무
+슨</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -4469,7 +4476,8 @@
       </c>
       <c r="O11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">한아</t>
+          <t xml:space="preserve">한
+아</t>
         </is>
       </c>
       <c r="P11" s="21"/>
@@ -4526,7 +4534,8 @@
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">숨에</t>
+          <t xml:space="preserve">숨
+에</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -4640,7 +4649,8 @@
       </c>
       <c r="M15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">무슨</t>
+          <t xml:space="preserve">무
+슨</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -4651,7 +4661,8 @@
       </c>
       <c r="O15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃을</t>
+          <t xml:space="preserve">꽃
+을</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -4761,7 +4772,8 @@
       </c>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">짝에</t>
+          <t xml:space="preserve">짝
+에</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -448,7 +448,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -458,7 +457,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -468,7 +466,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -479,7 +476,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -489,7 +485,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -500,7 +495,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -510,7 +504,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -521,7 +514,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -535,7 +527,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -546,7 +537,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -560,7 +550,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -571,7 +560,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -589,7 +577,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -600,7 +587,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -614,7 +600,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -625,7 +610,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -639,7 +623,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -649,7 +632,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -659,7 +641,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -670,7 +651,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -684,7 +664,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -695,7 +674,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -717,7 +695,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -728,7 +705,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -747,7 +723,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -758,7 +733,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -772,7 +746,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -783,7 +756,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -797,7 +769,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -807,7 +778,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -818,7 +788,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -827,7 +796,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -838,7 +806,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -849,7 +816,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -868,7 +834,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -877,17 +843,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -920,6 +886,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1012,7 +984,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1070,6 +1042,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4221,355 +4237,355 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7" t="s">
+      <c r="B3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
+      <c r="F4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="22"/>
+      <c r="J4" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7" t="s">
+      <c r="H5" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="8"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="7" t="s">
+      <c r="F6" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="9" t="s">
+      <c r="I6" s="22"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="11"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7" t="s">
+      <c r="F7" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="9" t="s">
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="8"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="7" t="s">
+      <c r="F8" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="22"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="11"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="7" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7" t="s">
+      <c r="F9" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="19" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="7" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="24"/>
+      <c r="H10" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="14" t="s">
+      <c r="I10" s="24"/>
+      <c r="J10" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="24"/>
+      <c r="L10" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="13" t="s">
+      <c r="Q10" s="24" t="s">
         <v>165</v>
       </c>
     </row>

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -908,10 +908,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -446,125 +446,41 @@
 고</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌汰</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">㴌汰
+㴌汰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰
+汰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">汰
 無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㳞
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+㳞</t>
   </si>
   <si>
     <t xml:space="preserve">궁
 초</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+    <t xml:space="preserve">㳞
 㳞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">으
 며</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰
+    <t xml:space="preserve">汰
 㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+汰</t>
   </si>
   <si>
     <t xml:space="preserve">댕
@@ -575,145 +491,35 @@
 두</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+    <t xml:space="preserve">㴌
 汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">오
 리</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">無
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+南</t>
   </si>
   <si>
     <t xml:space="preserve">비
 올</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲
+    <t xml:space="preserve">–
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仲
 仲
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">때
 는</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">무
-슨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">한
-아</t>
-  </si>
-  <si>
-    <t xml:space="preserve">숨
-에</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">짝
-에</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -721,106 +527,62 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">무
+슨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한
+아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숨
+에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無
+南
+仲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">짝
+에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無
 無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無
+無
+無</t>
   </si>
   <si>
     <t xml:space="preserve">꽃
 을</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+    <t xml:space="preserve">㳞
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
+湳</t>
   </si>
   <si>
     <t xml:space="preserve">단
 장</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">㴌汰
+無
 –</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
+  </si>
+  <si>
+    <t xml:space="preserve">汰
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 㳞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+㴌</t>
   </si>
   <si>
     <t xml:space="preserve">하
@@ -4228,7 +3990,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B2:Q10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -4252,7 +4014,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4272,7 +4035,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>65</v>
       </c>
@@ -4320,7 +4083,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>65</v>
       </c>
@@ -4364,7 +4127,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>65</v>
       </c>
@@ -4402,7 +4165,7 @@
       <c r="P5" s="18"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>148</v>
       </c>
@@ -4438,7 +4201,7 @@
       <c r="P6" s="18"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
       <c r="D7" s="18" t="s">
@@ -4474,7 +4237,7 @@
       <c r="P7" s="18"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B8" s="18"/>
       <c r="C8" s="22"/>
       <c r="D8" s="18" t="s">
@@ -4508,7 +4271,7 @@
       <c r="P8" s="18"/>
       <c r="Q8" s="22"/>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B9" s="18"/>
       <c r="C9" s="19"/>
       <c r="D9" s="18" t="s">
@@ -4546,7 +4309,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
       <c r="B10" s="18"/>
       <c r="C10" s="24"/>
       <c r="D10" s="18" t="s">
@@ -4586,21 +4349,13 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" ht="82.06" customHeight="true"/>
-    <row r="12" ht="82.06" customHeight="true"/>
-    <row r="13" ht="82.06" customHeight="true"/>
-    <row r="14" ht="82.06" customHeight="true"/>
-    <row r="15" ht="82.06" customHeight="true"/>
-    <row r="16" ht="82.06" customHeight="true"/>
-    <row r="17" ht="82.06" customHeight="true"/>
-    <row r="18" ht="82.06" customHeight="true"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:Q2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/궁초댕기.xlsx
+++ b/sheets/민요/검수/궁초댕기.xlsx
@@ -3996,26 +3996,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4035,7 +4035,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>65</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>65</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>65</v>
       </c>
@@ -4165,7 +4165,7 @@
       <c r="P5" s="18"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>148</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="P6" s="18"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
       <c r="D7" s="18" t="s">
@@ -4237,7 +4237,7 @@
       <c r="P7" s="18"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B8" s="18"/>
       <c r="C8" s="22"/>
       <c r="D8" s="18" t="s">
@@ -4271,7 +4271,7 @@
       <c r="P8" s="18"/>
       <c r="Q8" s="22"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B9" s="18"/>
       <c r="C9" s="19"/>
       <c r="D9" s="18" t="s">
@@ -4309,7 +4309,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="154.07" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="144.08" customHeight="true">
       <c r="B10" s="18"/>
       <c r="C10" s="24"/>
       <c r="D10" s="18" t="s">
@@ -4355,7 +4355,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
